--- a/output/2026-09-03_01_Italia_Campania_Depolverazione_Trattamento_aria.xlsx
+++ b/output/2026-09-03_01_Italia_Campania_Depolverazione_Trattamento_aria.xlsx
@@ -493,8 +493,6 @@
           <t>Depolverazione / Trattamento aria</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
           <t>Impianti di aspirazione, filtrazione, depolverazione e bonifica ambientale industriale (attiva dal 1944); reparto engineering e officina propria, specializzazione filtri ATEX. Verificata via sito ufficiale brunobalducci.com, poolindustriale.it, b2bindustry.net.</t>
@@ -532,7 +530,6 @@
           <t>081 0484254 / 327 6553900 / 334 5499050</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
           <t>Progettazione, realizzazione e manutenzione di condotti metallici/canalizzazioni per impianti di condizionamento, aspirazione e termoventilazione industriale; filtraggio fumi. Verificata via sagiclima.eu, paginegialle.it, paginebianche.it, europages.it. Indirizzo: Strada Provinciale delle Brecce 51, Napoli.</t>
@@ -570,7 +567,6 @@
           <t>081 5771304</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
           <t>Canalizzazioni in lamiera zincata/inox, condotte di distribuzione aria, condotti a spirale per rimozione fumi/esalazioni, installazione UTA; carpenteria leggera a supporto dei condotti. Verificata via meridionemontaggi.it e reportaziende.it (P.IVA 08243681213).</t>
@@ -608,7 +604,6 @@
           <t>081 5969669</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
           <t>Cappe industriali ad alta efficienza per aspirazione fumi/vapori/odori, filtri a labirinto, filtri antigrasso, filtri a carboni attivi, sistemi wet scrubbing; anche abbattitori di fuliggine. Verificata via mcaimpianti.eu, mcaimpianti-napoli.it, paginebianche.it.</t>
@@ -752,7 +747,6 @@
           <t>GM Aspirazioni e Canne Fumarie</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr">
         <is>
           <t>Napoli</t>
@@ -768,7 +762,6 @@
           <t>081 0489141 / 333 1832771</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
           <t>Cappe aspiranti, unita' a carboni attivi, abbattitori di fuliggine, canne fumarie; impianti di trattamento aria anche per lavorazione pomodoro e fumi di saldatura in carrozzeria; opera su tutta la Campania. Verificata via paginebianche.it, paginegialle.it, virgilio.it. Indirizzo: Via Alberto Marghieri 49, Barra, Napoli.</t>
@@ -806,7 +799,6 @@
           <t>081 18360532</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
           <t>Abbattitori di fuliggine/fumi/odori per forni a legna (pizzerie, panificazione), unico marchio approvato dall'Associazione Verace Pizza Napoletana; 30 anni di esperienza nel trattamento emissioni gassose. Verificata via vtkful.it, infobuild.it, edilportale.com. Indirizzo: Via U. Migliaccio, Marano di Napoli (NA).</t>
@@ -886,7 +878,6 @@
           <t>089 955212</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
           <t>Progettazione, costruzione e installazione di impianti di aspirazione aria/fumi, filtrazione, ventilazione, abbattimento acustico e depurazione acque. Verificata via euroair.it ed euroairsrl.com. Sede: Via Giustino Fortunato 25, Baronissi (SA).</t>
@@ -924,7 +915,6 @@
           <t>089 301662</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
           <t>Forniture industriali attiva dal 2002: gruppi trattamento aria compressa, pneumatica, filtri, compressori, cuscinetti, trasmissioni. Verificata via mediterraneaservicesrl.com, paginegialle.it, durevoli.com. Sede: Via delle Calabrie 33/B, Salerno.</t>
@@ -969,7 +959,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Sistemi di aspirazione e filtrazione aria industriale, aspirazione e trattamento polveri; opera anche su Napoli, Bari e Foggia. Verificata via geeicoengineering.com e gge.eu. Sede legale: Piazza Caduti Civili di Guerra 1, Salerno (sede operativa Baronissi, SA). Deduplicata: stessa azienda elencata erroneamente anche nella lista grezza di Napoli con indirizzo non confermato (voce scartata, vedi 'scartati').</t>
+          <t>Sistemi di aspirazione e filtrazione aria industriale, aspirazione e trattamento polveri; opera anche su Napoli, Bari e Foggia. Verificata via geeicoengineering.com e gge.eu. Sede legale: Piazza Caduti Civili di Guerra 1, Salerno (sede operativa Baronissi, SA). Deduplicata: stessa azienda elencata erroneamente anche nella lista grezza di Napoli con indirizzo non confermato (voce scartata, vedi 'scartati'). [DUPLICATO — vedi anche: 2026-09-03_00_Italia_Campania_Cleaning.xlsx]</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1004,7 +994,6 @@
           <t>089 302937</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
           <t>Filtrazione, purificazione, separazione fluidi; carboni attivi, trattamento aria compressa, filtri per condizionamento (celle, tasche, assoluti), sistemi di dust abatement, maniche filtranti; fondata nel 1993. Verificata via sepcofiltri.it. Sede: Fraz. Fuorni, Salerno.</t>
@@ -1042,7 +1031,6 @@
           <t>081 5179335</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
           <t>Fornitura di articoli tecnici industriali (dal 1960): componenti pneumatici, raccordi aria, sezione dedicata al trattamento aria compressa, oltre a trasmissioni, cuscinetti e riduttori. Verificata via ugoformisano.com. Sede: Via Napoli 6, Nocera Inferiore (SA).</t>
@@ -1122,7 +1110,6 @@
           <t>324 8996189</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
           <t>Produzione, fornitura e installazione di abbattitori di fumi/fuliggine/odori (ad acqua atomizzata ad alta pressione) per forni a legna/gas/elettrici, cappe professionali, forni industriali e tostatura caffe'. Verificata via abbattitorizapper.it, Facebook, europages.it. Sede: Via Galileo Ferraris 24, Scafati (SA). Riassegnata da Caserta a Salerno: nella lista grezza di Caserta l'indirizzo era gia' correttamente segnalato come 'non in provincia di Caserta'.</t>
@@ -1209,7 +1196,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Impianti di depurazione inquinanti atmosferici, depolverazione, abbattimento fumi e solventi, aspirazione industriale, cabine di verniciatura. Verificata via virgilio.it aziende, misterimprese.it, registroaziende.it (P.IVA 01915560641). Sede: Localita' Piano Pezze / Via Tavernole, Manocalzati (AV); anche Atripalda (AV).</t>
+          <t>Impianti di depurazione inquinanti atmosferici, depolverazione, abbattimento fumi e solventi, aspirazione industriale, cabine di verniciatura. Verificata via virgilio.it aziende, misterimprese.it, registroaziende.it (P.IVA 01915560641). Sede: Localita' Piano Pezze / Via Tavernole, Manocalzati (AV); anche Atripalda (AV). [DUPLICATO — vedi anche: 2026-09-03_00_Italia_Campania_Cleaning.xlsx]</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1244,7 +1231,6 @@
           <t>0825 683611 (sede Avellino) / 0824 958307 (unita' operativa Sassinoro, BN)</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
           <t>Impianti di aspirazione, ventilazione, condizionamento, filtrazione e purificazione aria industriale, dal 1994. Verificata via atoka.io, reportaziende.it (P.IVA 01927650646), paginebianche.it, paginegialle.it. Sede legale: Piazza D'Armi 19, Avellino (AV); unita' operativa: Contrada Pianella, Sassinoro (BN). Deduplicata: azienda unica, assegnata alla provincia della sede legale (Avellino); nella lista grezza di Benevento era elencata come voce separata (scartata come duplicato, vedi 'scartati').</t>
@@ -1282,7 +1268,6 @@
           <t>0825 968300 / 848800331</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
           <t>Impianti centralizzati di aspirazione polveri industriali, impianti di filtrazione ecologici, depuratori d'aria. Verificata via misterimprese.it e gramm-energy.it (linea industriale distinta da 'Gramm Power SpA', che tratta aspirapolvere per uso domestico con marchio dello stesso gruppo). Sede: Contrada Cardogna, Area PIP, Montemiletto (AV).</t>
@@ -1300,7 +1285,6 @@
           <t>Delta Aspiratori S.r.l.</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr"/>
       <c r="C23" t="inlineStr">
         <is>
           <t>Avellino</t>
@@ -1311,8 +1295,6 @@
           <t>Depolverazione / Trattamento aria</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
           <t>Esistenza confermata in registro camerale (P.IVA 02093440648, attiva dal 20/02/1998, ATECO 28.29.9 - fabbricazione di altre macchine di impiego generale). Indirizzo Piazza d'Armi 19, Avellino (AV): coincide con la sede legale di SIA Impianti Aeromeccanici - verosimilmente azienda collegata/di famiglia allo stesso gruppo. Nessun sito, telefono, email o dettaglio sui prodotti reperiti online: dati commerciali da verificare direttamente prima di un contatto B2B.</t>
@@ -1345,8 +1327,6 @@
           <t>Depolverazione / Trattamento aria</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
           <t>Rivenditore e centro assistenza autorizzato compressori Atlas Copco, Ceccato, Mark, Abac, Alup, Balma; opera su Avellino, Benevento, Caserta, Napoli e Salerno. Verificata via misterimprese.it, Facebook, limpresa.it. Sede: Avellino (AV). Riassegnata da Benevento (dove appariva nella lista grezza) ad Avellino, provincia della sede.</t>
@@ -1384,10 +1364,9 @@
           <t>0824 42448 / 0824 21911 / 0824 25811</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Forniture industriali: ferramenta, aspiratori e aspiracenere, utensileria elettrica, pulizia industriale e civile; azienda fondata nel 1929. Verificata via sidersan.com, store.sidersan.com, Facebook. Sede legale a Roma; sede/negozio operativo a Via Valfortore 2, Benevento (BN), dove e' storicamente insediata e attiva sul mercato locale.</t>
+          <t>Forniture industriali: ferramenta, aspiratori e aspiracenere, utensileria elettrica, pulizia industriale e civile; azienda fondata nel 1929. Verificata via sidersan.com, store.sidersan.com, Facebook. Sede legale a Roma; sede/negozio operativo a Via Valfortore 2, Benevento (BN), dove e' storicamente insediata e attiva sul mercato locale. [DUPLICATO — vedi anche: 2026-09-03_00_Italia_Campania_Cleaning.xlsx]</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1402,7 +1381,6 @@
           <t>Q-TEC S.R.L. (QTS)</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr"/>
       <c r="C26" t="inlineStr">
         <is>
           <t>Caserta</t>
@@ -1413,8 +1391,6 @@
           <t>Depolverazione / Trattamento aria</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
           <t>Impianti di aspirazione fumi/polveri industriali, aspirazione centralizzata, progettazione impianti di aspirazione polveri; classificata anche come commercio all'ingrosso di altre macchine per industria. Verificata via europages.it (categoria: 'Aspirazione di fumo - Impianti') e informazione-aziende.it. Sede: Via Galileo Galilei 8, Caserta (CE).</t>
@@ -1452,7 +1428,6 @@
           <t>0823 621810</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
           <t>Vendita e assistenza compressori a vite/a pistoni, aspiratori industriali, idropulitrici; opera su Caserta, Napoli, Avellino e Benevento. Verificata via tecnoariacompressori.it, virgilio.it aziende, aziendit.com (P.IVA 02772950610). Sede: Via Fuori Porta Roma 188, Capua (CE).</t>
@@ -1470,7 +1445,6 @@
           <t>AR Aspirazioni (di Ramaglia Antonio)</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr"/>
       <c r="C28" t="inlineStr">
         <is>
           <t>Caserta</t>
@@ -1486,7 +1460,6 @@
           <t>392 0172330</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
           <t>Impianti di aspirazione, cappe cucina, unita' a carboni attivi, abbattitori di fuliggine, canne fumarie. Esistenza e attivita' confermate tramite ricerca (titolare Ramaglia Antonio). Sede: Via Alcide De Gasperi 43, Orta di Atella (CE). Sito web e email non reperiti.</t>

--- a/output/2026-09-03_01_Italia_Campania_Depolverazione_Trattamento_aria.xlsx
+++ b/output/2026-09-03_01_Italia_Campania_Depolverazione_Trattamento_aria.xlsx
@@ -500,7 +500,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/09/2026)</t>
         </is>
       </c>
     </row>
@@ -537,7 +537,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/09/2026)</t>
         </is>
       </c>
     </row>
@@ -574,7 +574,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/09/2026)</t>
         </is>
       </c>
     </row>
@@ -611,7 +611,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/09/2026)</t>
         </is>
       </c>
     </row>
@@ -653,7 +653,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/09/2026)</t>
         </is>
       </c>
     </row>
@@ -695,7 +695,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/09/2026)</t>
         </is>
       </c>
     </row>
@@ -737,7 +737,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/09/2026)</t>
         </is>
       </c>
     </row>
@@ -769,7 +769,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/09/2026)</t>
         </is>
       </c>
     </row>
@@ -806,7 +806,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/09/2026)</t>
         </is>
       </c>
     </row>
@@ -848,7 +848,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/09/2026)</t>
         </is>
       </c>
     </row>
@@ -885,7 +885,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/09/2026)</t>
         </is>
       </c>
     </row>
@@ -922,7 +922,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/09/2026)</t>
         </is>
       </c>
     </row>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/09/2026)</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/09/2026)</t>
         </is>
       </c>
     </row>
@@ -1117,7 +1117,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/09/2026)</t>
         </is>
       </c>
     </row>
@@ -1159,7 +1159,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/09/2026)</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/09/2026)</t>
         </is>
       </c>
     </row>
@@ -1275,7 +1275,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/09/2026)</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/09/2026)</t>
         </is>
       </c>
     </row>
@@ -1398,7 +1398,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/09/2026)</t>
         </is>
       </c>
     </row>
